--- a/basedatos_partidas/salida/descompuestos/07.01.01.060.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.01.01.060.xlsx
@@ -584,10 +584,10 @@
         <v>0.1</v>
       </c>
       <c r="G11" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12">
@@ -688,10 +688,10 @@
         <v>0.05</v>
       </c>
       <c r="G15" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>10.82</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="17">
@@ -847,7 +847,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>14.58</v>
+        <v>14.67</v>
       </c>
       <c r="H25" t="n">
         <v>0.15</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>14.73</v>
+        <v>14.82</v>
       </c>
     </row>
   </sheetData>
